--- a/output/pdf_financials_xlsx/AMX.xlsx
+++ b/output/pdf_financials_xlsx/AMX.xlsx
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.019006</v>
+        <v>-1.284334</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.131625</v>
+        <v>-1.305923</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.632664</v>
+        <v>-0.632664</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.587149</v>
+        <v>-0.587149</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.632664</v>
+        <v>-0.632664</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.587149</v>
+        <v>-0.587149</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-21.0888</v>
+        <v>21.0888</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-29.35745</v>
+        <v>29.35745</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.916506820936978</v>
+        <v>197.083493179063</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>18.31243200227053</v>
+        <v>181.6875679977295</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.632664</v>
+        <v>-0.632664</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.587149</v>
+        <v>-0.587149</v>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
@@ -19496,10 +19496,10 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.632664</v>
+        <v>-0.632664</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0.587149</v>
+        <v>-0.587149</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -19842,10 +19842,10 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.601414</v>
+        <v>-0.601414</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.649274</v>
+        <v>-0.649274</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
